--- a/database/Nook_ePOS_Database_Template_1_0_6.xlsx
+++ b/database/Nook_ePOS_Database_Template_1_0_6.xlsx
@@ -2,21 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="R29039cec10cc42dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="R3348e6f95d4743f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="3" r:id="Recd5b7f459b04a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MenuItems" sheetId="4" r:id="R54ab1a02460a4687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="5" r:id="R5bffa334f0d8405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PromptOptions" sheetId="6" r:id="R16d3c316b998402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="7" r:id="R1983972115bc4e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TicketItems" sheetId="8" r:id="R3f833fc74a5d4a82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TicketAddOns" sheetId="9" r:id="R1d314aaf5f054180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KitchenQueue" sheetId="10" r:id="Re6e59b8b30d0401f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HeldOrders" sheetId="11" r:id="Rcd8077ba0f314abf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refunds" sheetId="12" r:id="R44262abd3c6049d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="13" r:id="R90ff7214609b4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="14" r:id="Rc713754bf7594b27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeletedItems" sheetId="15" r:id="R5113c05feb814993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="R3338ee7f30634dc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="2" r:id="Rd9fcccd4f78c4eab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories" sheetId="3" r:id="R037efed26ef14186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MenuItems" sheetId="4" r:id="R833af74a626d421c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompts" sheetId="5" r:id="R77e62d67e34b4bdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PromptOptions" sheetId="6" r:id="R07a248ed3a264119"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tickets" sheetId="7" r:id="R178a79060894466f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TicketItems" sheetId="8" r:id="R4f940a08212c4e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TicketAddOns" sheetId="9" r:id="R9b415d77556e4877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KitchenQueue" sheetId="10" r:id="R586c9cfd0add4c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HeldOrders" sheetId="11" r:id="R37ad10df020843b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refunds" sheetId="12" r:id="R49afeaec430b4157"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AuditLog" sheetId="13" r:id="R3f926bbfa6db4e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="14" r:id="R62b3c5f2ee3f45c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DeletedItems" sheetId="15" r:id="R0c8b6ae98854414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefundItems" sheetId="16" r:id="R00e922df0cf74291"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReceiptEmails" sheetId="17" r:id="R7a6c604bf61d47b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -78,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="22">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -131,6 +133,12 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -336,7 +344,7 @@
         <x:v>FrontendVersion</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>1.0.6</x:v>
+        <x:v>3.13.16</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -344,7 +352,7 @@
         <x:v>BackendVersion</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>1.0.6</x:v>
+        <x:v>3.13.16</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -360,7 +368,23 @@
         <x:v>BuildDate</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>2026-07-04</x:v>
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>NextTicketNumber</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>KitchenRevision</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -477,35 +501,43 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="7.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="6.75" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.25" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="6.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="6.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="6.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19.3799991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="22" t="str">
         <x:v>RefundID</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="22" t="str">
+        <x:v>RefundNumber</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
         <x:v>TicketID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="D1" s="22" t="str">
         <x:v>TicketNumber</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="E1" s="22" t="str">
         <x:v>CreatedAt</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="F1" s="22" t="str">
         <x:v>Amount</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="G1" s="22" t="str">
         <x:v>Reason</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="H1" s="23" t="str">
         <x:v>StaffName</x:v>
+      </x:c>
+      <x:c r="I1" s="23" t="str">
+        <x:v>OriginalPaymentMethod</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -664,6 +696,108 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="7.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="5.75" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="7.25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12.880000114440918" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="23" t="str">
+        <x:v>RefundItemID</x:v>
+      </x:c>
+      <x:c r="B1" s="23" t="str">
+        <x:v>RefundID</x:v>
+      </x:c>
+      <x:c r="C1" s="23" t="str">
+        <x:v>TicketID</x:v>
+      </x:c>
+      <x:c r="D1" s="23" t="str">
+        <x:v>TicketItemID</x:v>
+      </x:c>
+      <x:c r="E1" s="23" t="str">
+        <x:v>ItemID</x:v>
+      </x:c>
+      <x:c r="F1" s="23" t="str">
+        <x:v>ItemName</x:v>
+      </x:c>
+      <x:c r="G1" s="23" t="str">
+        <x:v>CategoryID</x:v>
+      </x:c>
+      <x:c r="H1" s="23" t="str">
+        <x:v>Quantity</x:v>
+      </x:c>
+      <x:c r="I1" s="23" t="str">
+        <x:v>UnitRefundAmount</x:v>
+      </x:c>
+      <x:c r="J1" s="23" t="str">
+        <x:v>LineRefundTotal</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="8.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.5" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="5.25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.380000114440918" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="23" t="str">
+        <x:v>ReceiptEmailID</x:v>
+      </x:c>
+      <x:c r="B1" s="23" t="str">
+        <x:v>CreatedAt</x:v>
+      </x:c>
+      <x:c r="C1" s="23" t="str">
+        <x:v>TicketID</x:v>
+      </x:c>
+      <x:c r="D1" s="23" t="str">
+        <x:v>TicketNumber</x:v>
+      </x:c>
+      <x:c r="E1" s="23" t="str">
+        <x:v>RecipientEmail</x:v>
+      </x:c>
+      <x:c r="F1" s="23" t="str">
+        <x:v>StaffName</x:v>
+      </x:c>
+      <x:c r="G1" s="23" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="H1" s="23" t="str">
+        <x:v>ErrorMessage</x:v>
+      </x:c>
+      <x:c r="I1" s="23" t="str">
+        <x:v>RemainingQuota</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -697,39 +831,55 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
-        <x:v>LastConfirmedScriptUrl</x:v>
-      </x:c>
-      <x:c r="B3" t="str"/>
+        <x:v>KitchenDisplayEnabled</x:v>
+      </x:c>
+      <x:c r="B3" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
-        <x:v>LastConfirmedUrlVersion</x:v>
-      </x:c>
-      <x:c r="B4" t="str"/>
+        <x:v>KitchenPromptTitlesEnabled</x:v>
+      </x:c>
+      <x:c r="B4" t="str">
+        <x:v>TRUE</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="str">
-        <x:v>LastConfirmedUrlSavedAt</x:v>
+        <x:v>LastConfirmedScriptUrl</x:v>
       </x:c>
       <x:c r="B5" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="str">
-        <x:v>LastConfirmedUrlFrontendVersion</x:v>
+        <x:v>LastConfirmedUrlVersion</x:v>
       </x:c>
       <x:c r="B6" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="str">
-        <x:v>LastConfirmedUrlBackendVersion</x:v>
+        <x:v>LastConfirmedUrlSavedAt</x:v>
       </x:c>
       <x:c r="B7" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="str">
+        <x:v>LastConfirmedUrlFrontendVersion</x:v>
+      </x:c>
+      <x:c r="B8" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>LastConfirmedUrlBackendVersion</x:v>
+      </x:c>
+      <x:c r="B9" t="str"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
         <x:v>LastConfirmedUrlDatabaseVersion</x:v>
       </x:c>
-      <x:c r="B8" t="str"/>
+      <x:c r="B10" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
